--- a/Estudos.xlsx
+++ b/Estudos.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -154,6 +154,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -392,8 +395,8 @@
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3">
-        <v>33.0</v>
+      <c r="C2" s="4">
+        <v>8.0</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -406,8 +409,8 @@
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3">
-        <v>17.0</v>
+      <c r="C3" s="4">
+        <v>28.0</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -420,8 +423,8 @@
       <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3">
-        <v>27.0</v>
+      <c r="C4" s="4">
+        <v>70.0</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
@@ -434,8 +437,8 @@
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3">
-        <v>18.0</v>
+      <c r="C5" s="4">
+        <v>23.0</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
@@ -448,8 +451,8 @@
       <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3">
-        <v>33.0</v>
+      <c r="C6" s="4">
+        <v>8.0</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
@@ -462,8 +465,8 @@
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3">
-        <v>29.0</v>
+      <c r="C7" s="4">
+        <v>8.0</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
@@ -476,8 +479,8 @@
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="3">
-        <v>17.0</v>
+      <c r="C8" s="4">
+        <v>8.0</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
@@ -490,8 +493,8 @@
       <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="3">
-        <v>35.0</v>
+      <c r="C9" s="4">
+        <v>16.0</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -504,8 +507,8 @@
       <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="3">
-        <v>15.0</v>
+      <c r="C10" s="4">
+        <v>16.0</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -518,8 +521,8 @@
       <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="3">
-        <v>48.0</v>
+      <c r="C11" s="4">
+        <v>16.0</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>24</v>
